--- a/IIM_Ranchi_MBA_Timetable.xlsx
+++ b/IIM_Ranchi_MBA_Timetable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kishore/Downloads/Term3/OR/WAI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407CA2C4-1BFA-2A49-991C-1EBE7F0E7B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59104E1-AD34-5441-B998-7DD56924D86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-1960" windowWidth="38400" windowHeight="21600" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Master Timetable" sheetId="1" r:id="rId1"/>
